--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/MISSISSIPPI_2015.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/MISSISSIPPI_2015.xlsx
@@ -1932,7 +1932,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C88">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C177">
